--- a/ig/DM-MAI-2026/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/ig/DM-MAI-2026/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1027,6 +1027,54 @@
   </si>
   <si>
     <t>Espace de consommation de drogues à fumer</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Appareil de thermoformage</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Appareil de thermosoudage</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Plateforme de force (étude de la posture)</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>Plateforme de pression (étude de la marche)</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>Piste de marche</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Tapis de course</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Système vidéo d'analyse de la marche et de la course</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>Semelles avec capteurs embarqués</t>
   </si>
   <si>
     <t/>
@@ -1297,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2557,15 +2605,79 @@
         <v>338</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
